--- a/概要とxcf/概要/ガントチャート_お茶.xlsx
+++ b/概要とxcf/概要/ガントチャート_お茶.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A33D864-F09B-4146-9673-C4496FA35DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CF167F-4DD6-4E6E-9925-3CE57E4321D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="645" windowWidth="21600" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1845" yWindow="990" windowWidth="21600" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="進捗確認表" sheetId="19" r:id="rId1"/>
@@ -1758,6 +1758,40 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1777,45 +1811,11 @@
     <xf numFmtId="182" fontId="1" fillId="0" borderId="18" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2477,11 +2477,11 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="102">
+      <c r="E1" s="112">
         <v>46125</v>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
       <c r="Q1" s="108" t="s">
         <v>2</v>
       </c>
@@ -2494,207 +2494,207 @@
       <c r="BT1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="CD1" s="111" t="s">
+      <c r="CD1" s="110" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:375" x14ac:dyDescent="0.45">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
       <c r="Q2" s="108"/>
       <c r="AP2" s="108"/>
       <c r="AZ2" s="108"/>
       <c r="BT2" s="108"/>
-      <c r="CD2" s="111"/>
+      <c r="CD2" s="110"/>
     </row>
     <row r="3" spans="1:375" x14ac:dyDescent="0.45">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
       <c r="Q3" s="108"/>
       <c r="AP3" s="108"/>
       <c r="AZ3" s="108"/>
       <c r="BT3" s="108"/>
-      <c r="CD3" s="111"/>
+      <c r="CD3" s="110"/>
     </row>
     <row r="4" spans="1:375" x14ac:dyDescent="0.45">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
       <c r="Q4" s="109"/>
       <c r="AP4" s="109"/>
       <c r="AZ4" s="109"/>
       <c r="BT4" s="109"/>
-      <c r="CD4" s="112"/>
+      <c r="CD4" s="111"/>
     </row>
     <row r="5" spans="1:375" x14ac:dyDescent="0.45">
       <c r="A5" s="70"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="110">
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="107">
         <f>H6</f>
         <v>46125</v>
       </c>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110">
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107">
         <f>H5+7</f>
         <v>46132</v>
       </c>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110">
+      <c r="N5" s="107"/>
+      <c r="O5" s="107"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="107">
         <f>M5+7</f>
         <v>46139</v>
       </c>
-      <c r="S5" s="110"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="110"/>
-      <c r="W5" s="110">
+      <c r="S5" s="107"/>
+      <c r="T5" s="107"/>
+      <c r="U5" s="107"/>
+      <c r="V5" s="107"/>
+      <c r="W5" s="107">
         <f>R5+7</f>
         <v>46146</v>
       </c>
-      <c r="X5" s="110"/>
-      <c r="Y5" s="110"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="110"/>
-      <c r="AB5" s="110">
+      <c r="X5" s="107"/>
+      <c r="Y5" s="107"/>
+      <c r="Z5" s="107"/>
+      <c r="AA5" s="107"/>
+      <c r="AB5" s="107">
         <f>W5+7</f>
         <v>46153</v>
       </c>
-      <c r="AC5" s="110"/>
-      <c r="AD5" s="110"/>
-      <c r="AE5" s="110"/>
-      <c r="AF5" s="110"/>
-      <c r="AG5" s="110">
+      <c r="AC5" s="107"/>
+      <c r="AD5" s="107"/>
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="107">
         <f>AB5+7</f>
         <v>46160</v>
       </c>
-      <c r="AH5" s="110"/>
-      <c r="AI5" s="110"/>
-      <c r="AJ5" s="110"/>
-      <c r="AK5" s="110"/>
-      <c r="AL5" s="110">
+      <c r="AH5" s="107"/>
+      <c r="AI5" s="107"/>
+      <c r="AJ5" s="107"/>
+      <c r="AK5" s="107"/>
+      <c r="AL5" s="107">
         <f>AG5+7</f>
         <v>46167</v>
       </c>
-      <c r="AM5" s="110"/>
-      <c r="AN5" s="110"/>
-      <c r="AO5" s="110"/>
-      <c r="AP5" s="110"/>
-      <c r="AQ5" s="110">
+      <c r="AM5" s="107"/>
+      <c r="AN5" s="107"/>
+      <c r="AO5" s="107"/>
+      <c r="AP5" s="107"/>
+      <c r="AQ5" s="107">
         <f>AL5+7</f>
         <v>46174</v>
       </c>
-      <c r="AR5" s="110"/>
-      <c r="AS5" s="110"/>
-      <c r="AT5" s="110"/>
-      <c r="AU5" s="110"/>
-      <c r="AV5" s="110">
+      <c r="AR5" s="107"/>
+      <c r="AS5" s="107"/>
+      <c r="AT5" s="107"/>
+      <c r="AU5" s="107"/>
+      <c r="AV5" s="107">
         <f>AQ5+7</f>
         <v>46181</v>
       </c>
-      <c r="AW5" s="110"/>
-      <c r="AX5" s="110"/>
-      <c r="AY5" s="110"/>
-      <c r="AZ5" s="110"/>
-      <c r="BA5" s="110">
+      <c r="AW5" s="107"/>
+      <c r="AX5" s="107"/>
+      <c r="AY5" s="107"/>
+      <c r="AZ5" s="107"/>
+      <c r="BA5" s="107">
         <f>AV5+7</f>
         <v>46188</v>
       </c>
-      <c r="BB5" s="110"/>
-      <c r="BC5" s="110"/>
-      <c r="BD5" s="110"/>
-      <c r="BE5" s="110"/>
-      <c r="BF5" s="110">
+      <c r="BB5" s="107"/>
+      <c r="BC5" s="107"/>
+      <c r="BD5" s="107"/>
+      <c r="BE5" s="107"/>
+      <c r="BF5" s="107">
         <f>BA5+7</f>
         <v>46195</v>
       </c>
-      <c r="BG5" s="110"/>
-      <c r="BH5" s="110"/>
-      <c r="BI5" s="110"/>
-      <c r="BJ5" s="110"/>
-      <c r="BK5" s="110">
+      <c r="BG5" s="107"/>
+      <c r="BH5" s="107"/>
+      <c r="BI5" s="107"/>
+      <c r="BJ5" s="107"/>
+      <c r="BK5" s="107">
         <f>BF5+7</f>
         <v>46202</v>
       </c>
-      <c r="BL5" s="110"/>
-      <c r="BM5" s="110"/>
-      <c r="BN5" s="110"/>
-      <c r="BO5" s="110"/>
-      <c r="BP5" s="110">
+      <c r="BL5" s="107"/>
+      <c r="BM5" s="107"/>
+      <c r="BN5" s="107"/>
+      <c r="BO5" s="107"/>
+      <c r="BP5" s="107">
         <f>BK5+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ5" s="110"/>
-      <c r="BR5" s="110"/>
-      <c r="BS5" s="110"/>
-      <c r="BT5" s="110"/>
-      <c r="BU5" s="110">
+      <c r="BQ5" s="107"/>
+      <c r="BR5" s="107"/>
+      <c r="BS5" s="107"/>
+      <c r="BT5" s="107"/>
+      <c r="BU5" s="107">
         <f>BP5+7</f>
         <v>46216</v>
       </c>
-      <c r="BV5" s="110"/>
-      <c r="BW5" s="110"/>
-      <c r="BX5" s="110"/>
-      <c r="BY5" s="110"/>
-      <c r="BZ5" s="110">
+      <c r="BV5" s="107"/>
+      <c r="BW5" s="107"/>
+      <c r="BX5" s="107"/>
+      <c r="BY5" s="107"/>
+      <c r="BZ5" s="107">
         <f>BU5+7</f>
         <v>46223</v>
       </c>
-      <c r="CA5" s="110"/>
-      <c r="CB5" s="110"/>
-      <c r="CC5" s="110"/>
-      <c r="CD5" s="110"/>
-      <c r="CE5" s="110">
+      <c r="CA5" s="107"/>
+      <c r="CB5" s="107"/>
+      <c r="CC5" s="107"/>
+      <c r="CD5" s="107"/>
+      <c r="CE5" s="107">
         <f>BZ5+7</f>
         <v>46230</v>
       </c>
-      <c r="CF5" s="110"/>
-      <c r="CG5" s="110"/>
-      <c r="CH5" s="110"/>
-      <c r="CI5" s="110"/>
+      <c r="CF5" s="107"/>
+      <c r="CG5" s="107"/>
+      <c r="CH5" s="107"/>
+      <c r="CI5" s="107"/>
     </row>
     <row r="6" spans="1:375" x14ac:dyDescent="0.45">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="66"/>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="115" t="s">
+      <c r="E6" s="105"/>
+      <c r="F6" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="114"/>
+      <c r="G6" s="105"/>
       <c r="H6" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -3825,22 +3825,22 @@
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
       <c r="P13" s="77"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
-      <c r="U13" s="118"/>
-      <c r="V13" s="118"/>
-      <c r="W13" s="118"/>
-      <c r="X13" s="118"/>
-      <c r="Y13" s="118"/>
-      <c r="Z13" s="118"/>
-      <c r="AA13" s="119"/>
-      <c r="AB13" s="119"/>
-      <c r="AC13" s="119"/>
-      <c r="AD13" s="119"/>
-      <c r="AE13" s="119"/>
-      <c r="AF13" s="119"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="102"/>
+      <c r="V13" s="102"/>
+      <c r="W13" s="102"/>
+      <c r="X13" s="102"/>
+      <c r="Y13" s="102"/>
+      <c r="Z13" s="102"/>
+      <c r="AA13" s="103"/>
+      <c r="AB13" s="103"/>
+      <c r="AC13" s="103"/>
+      <c r="AD13" s="103"/>
+      <c r="AE13" s="103"/>
+      <c r="AF13" s="103"/>
       <c r="AG13" s="31"/>
       <c r="AH13" s="31"/>
       <c r="AI13" s="31"/>
@@ -4188,22 +4188,22 @@
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
       <c r="P14" s="77"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
-      <c r="U14" s="118"/>
-      <c r="V14" s="118"/>
-      <c r="W14" s="118"/>
-      <c r="X14" s="118"/>
-      <c r="Y14" s="118"/>
-      <c r="Z14" s="118"/>
-      <c r="AA14" s="119"/>
-      <c r="AB14" s="119"/>
-      <c r="AC14" s="119"/>
-      <c r="AD14" s="119"/>
-      <c r="AE14" s="119"/>
-      <c r="AF14" s="119"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="102"/>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="102"/>
+      <c r="Z14" s="102"/>
+      <c r="AA14" s="103"/>
+      <c r="AB14" s="103"/>
+      <c r="AC14" s="103"/>
+      <c r="AD14" s="103"/>
+      <c r="AE14" s="103"/>
+      <c r="AF14" s="103"/>
       <c r="AG14" s="31"/>
       <c r="AH14" s="31"/>
       <c r="AI14" s="31"/>
@@ -8096,7 +8096,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="54">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D25" s="55">
         <v>46147</v>
@@ -8455,7 +8455,7 @@
         <v>48</v>
       </c>
       <c r="C26" s="54">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D26" s="55">
         <v>46148</v>
@@ -8814,7 +8814,7 @@
         <v>48</v>
       </c>
       <c r="C27" s="54">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" s="55">
         <v>46151</v>
@@ -19512,6 +19512,23 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="30">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="Q1:Q4"/>
+    <mergeCell ref="CE5:CI5"/>
+    <mergeCell ref="BP5:BT5"/>
+    <mergeCell ref="BU5:BY5"/>
+    <mergeCell ref="BZ5:CD5"/>
+    <mergeCell ref="AP1:AP4"/>
+    <mergeCell ref="AZ1:AZ4"/>
+    <mergeCell ref="BT1:BT4"/>
+    <mergeCell ref="CD1:CD4"/>
+    <mergeCell ref="R5:V5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="BA5:BE5"/>
@@ -19525,23 +19542,6 @@
     <mergeCell ref="AV5:AZ5"/>
     <mergeCell ref="H5:L5"/>
     <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="Q1:Q4"/>
-    <mergeCell ref="CE5:CI5"/>
-    <mergeCell ref="BP5:BT5"/>
-    <mergeCell ref="BU5:BY5"/>
-    <mergeCell ref="BZ5:CD5"/>
-    <mergeCell ref="AP1:AP4"/>
-    <mergeCell ref="AZ1:AZ4"/>
-    <mergeCell ref="BT1:BT4"/>
-    <mergeCell ref="CD1:CD4"/>
-    <mergeCell ref="R5:V5"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F10:G10 G13 F29:G31 F14:G21 G22:G28 F37:F38 D37:D38">
@@ -19665,208 +19665,208 @@
       <c r="D1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="102">
+      <c r="E1" s="112">
         <v>46125</v>
       </c>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="103" t="s">
+      <c r="A3" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="70"/>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="110">
+      <c r="B6" s="114"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="107">
         <f>H7</f>
         <v>46125</v>
       </c>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110">
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107">
         <f>H6+7</f>
         <v>46132</v>
       </c>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110">
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="107">
         <f>M6+7</f>
         <v>46139</v>
       </c>
-      <c r="S6" s="110"/>
-      <c r="T6" s="110"/>
-      <c r="U6" s="110"/>
-      <c r="V6" s="110"/>
-      <c r="W6" s="110">
+      <c r="S6" s="107"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="107"/>
+      <c r="W6" s="107">
         <f>R6+7</f>
         <v>46146</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="110"/>
-      <c r="AB6" s="110">
+      <c r="X6" s="107"/>
+      <c r="Y6" s="107"/>
+      <c r="Z6" s="107"/>
+      <c r="AA6" s="107"/>
+      <c r="AB6" s="107">
         <f>W6+7</f>
         <v>46153</v>
       </c>
-      <c r="AC6" s="110"/>
-      <c r="AD6" s="110"/>
-      <c r="AE6" s="110"/>
-      <c r="AF6" s="110"/>
-      <c r="AG6" s="110">
+      <c r="AC6" s="107"/>
+      <c r="AD6" s="107"/>
+      <c r="AE6" s="107"/>
+      <c r="AF6" s="107"/>
+      <c r="AG6" s="107">
         <f>AB6+7</f>
         <v>46160</v>
       </c>
-      <c r="AH6" s="110"/>
-      <c r="AI6" s="110"/>
-      <c r="AJ6" s="110"/>
-      <c r="AK6" s="110"/>
-      <c r="AL6" s="110">
+      <c r="AH6" s="107"/>
+      <c r="AI6" s="107"/>
+      <c r="AJ6" s="107"/>
+      <c r="AK6" s="107"/>
+      <c r="AL6" s="107">
         <f>AG6+7</f>
         <v>46167</v>
       </c>
-      <c r="AM6" s="110"/>
-      <c r="AN6" s="110"/>
-      <c r="AO6" s="110"/>
-      <c r="AP6" s="110"/>
-      <c r="AQ6" s="110">
+      <c r="AM6" s="107"/>
+      <c r="AN6" s="107"/>
+      <c r="AO6" s="107"/>
+      <c r="AP6" s="107"/>
+      <c r="AQ6" s="107">
         <f>AL6+7</f>
         <v>46174</v>
       </c>
-      <c r="AR6" s="110"/>
-      <c r="AS6" s="110"/>
-      <c r="AT6" s="110"/>
-      <c r="AU6" s="110"/>
-      <c r="AV6" s="110">
+      <c r="AR6" s="107"/>
+      <c r="AS6" s="107"/>
+      <c r="AT6" s="107"/>
+      <c r="AU6" s="107"/>
+      <c r="AV6" s="107">
         <f>AQ6+7</f>
         <v>46181</v>
       </c>
-      <c r="AW6" s="110"/>
-      <c r="AX6" s="110"/>
-      <c r="AY6" s="110"/>
-      <c r="AZ6" s="110"/>
-      <c r="BA6" s="110">
+      <c r="AW6" s="107"/>
+      <c r="AX6" s="107"/>
+      <c r="AY6" s="107"/>
+      <c r="AZ6" s="107"/>
+      <c r="BA6" s="107">
         <f>AV6+7</f>
         <v>46188</v>
       </c>
-      <c r="BB6" s="110"/>
-      <c r="BC6" s="110"/>
-      <c r="BD6" s="110"/>
-      <c r="BE6" s="110"/>
-      <c r="BF6" s="110">
+      <c r="BB6" s="107"/>
+      <c r="BC6" s="107"/>
+      <c r="BD6" s="107"/>
+      <c r="BE6" s="107"/>
+      <c r="BF6" s="107">
         <f>BA6+7</f>
         <v>46195</v>
       </c>
-      <c r="BG6" s="110"/>
-      <c r="BH6" s="110"/>
-      <c r="BI6" s="110"/>
-      <c r="BJ6" s="110"/>
-      <c r="BK6" s="110">
+      <c r="BG6" s="107"/>
+      <c r="BH6" s="107"/>
+      <c r="BI6" s="107"/>
+      <c r="BJ6" s="107"/>
+      <c r="BK6" s="107">
         <f>BF6+7</f>
         <v>46202</v>
       </c>
-      <c r="BL6" s="110"/>
-      <c r="BM6" s="110"/>
-      <c r="BN6" s="110"/>
-      <c r="BO6" s="110"/>
-      <c r="BP6" s="110">
+      <c r="BL6" s="107"/>
+      <c r="BM6" s="107"/>
+      <c r="BN6" s="107"/>
+      <c r="BO6" s="107"/>
+      <c r="BP6" s="107">
         <f>BK6+7</f>
         <v>46209</v>
       </c>
-      <c r="BQ6" s="110"/>
-      <c r="BR6" s="110"/>
-      <c r="BS6" s="110"/>
-      <c r="BT6" s="110"/>
-      <c r="BU6" s="110">
+      <c r="BQ6" s="107"/>
+      <c r="BR6" s="107"/>
+      <c r="BS6" s="107"/>
+      <c r="BT6" s="107"/>
+      <c r="BU6" s="107">
         <f>BP6+7</f>
         <v>46216</v>
       </c>
-      <c r="BV6" s="110"/>
-      <c r="BW6" s="110"/>
-      <c r="BX6" s="110"/>
-      <c r="BY6" s="110"/>
-      <c r="BZ6" s="110">
+      <c r="BV6" s="107"/>
+      <c r="BW6" s="107"/>
+      <c r="BX6" s="107"/>
+      <c r="BY6" s="107"/>
+      <c r="BZ6" s="107">
         <f>BU6+7</f>
         <v>46223</v>
       </c>
-      <c r="CA6" s="110"/>
-      <c r="CB6" s="110"/>
-      <c r="CC6" s="110"/>
-      <c r="CD6" s="110"/>
-      <c r="CE6" s="110">
+      <c r="CA6" s="107"/>
+      <c r="CB6" s="107"/>
+      <c r="CC6" s="107"/>
+      <c r="CD6" s="107"/>
+      <c r="CE6" s="107">
         <f>BZ6+7</f>
         <v>46230</v>
       </c>
-      <c r="CF6" s="110"/>
-      <c r="CG6" s="110"/>
-      <c r="CH6" s="110"/>
-      <c r="CI6" s="110"/>
-      <c r="CJ6" s="110">
+      <c r="CF6" s="107"/>
+      <c r="CG6" s="107"/>
+      <c r="CH6" s="107"/>
+      <c r="CI6" s="107"/>
+      <c r="CJ6" s="107">
         <f>CE6+7</f>
         <v>46237</v>
       </c>
-      <c r="CK6" s="110"/>
-      <c r="CL6" s="110"/>
-      <c r="CM6" s="110"/>
-      <c r="CN6" s="110"/>
+      <c r="CK6" s="107"/>
+      <c r="CL6" s="107"/>
+      <c r="CM6" s="107"/>
+      <c r="CN6" s="107"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="65"/>
       <c r="B7" s="65"/>
       <c r="C7" s="66"/>
-      <c r="D7" s="113" t="s">
+      <c r="D7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="115" t="s">
+      <c r="E7" s="105"/>
+      <c r="F7" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="114"/>
+      <c r="G7" s="105"/>
       <c r="H7" s="67">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>46125</v>
@@ -22950,18 +22950,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -22978,6 +22966,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F15:G32">
@@ -23016,6 +23016,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C2961D859B1A8B4697EC07BF3C3DAD3B" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ab0ad3b8596db009aba937b3e43a8a7f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="02709b60-37ec-424b-b681-c6612ac7fe32" xmlns:ns3="f9048785-d070-4c78-8f2f-ed2b48eb345c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd157c9246152f7d64d090db49938ccd" ns2:_="" ns3:_="">
     <xsd:import namespace="02709b60-37ec-424b-b681-c6612ac7fe32"/>
@@ -23250,34 +23277,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
+    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="f9048785-d070-4c78-8f2f-ed2b48eb345c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="02709b60-37ec-424b-b681-c6612ac7fe32">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60750451-81D0-4123-9068-1385884A2A7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23294,23 +23313,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f9048785-d070-4c78-8f2f-ed2b48eb345c"/>
-    <ds:schemaRef ds:uri="02709b60-37ec-424b-b681-c6612ac7fe32"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>